--- a/course-design-2/outputs/tables/ch5/46_stage26_2_wording_consistency_audit.xlsx
+++ b/course-design-2/outputs/tables/ch5/46_stage26_2_wording_consistency_audit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_表述残留命中" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_统一口径建议" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="01_表述残留命中" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_统一统计范围建议" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,372 +426,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>文件</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>行号</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>命中类型</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>原文片段</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>15</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3,410 减少量行</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>主要结果如下。第一，岗位类别方面，岗位大类 12 个取值中 10 个、岗位细分类 78 个取值中 73 个在按字段校正后仍显著（q &lt; 0.05），算法方向细分类的“命中/未命中”薪资差异最大（|δ| 达 0.64），算法类岗位薪资中位数（275 元/天）明显高于运营、客服类（150～175 元/天）。第二，公司认证四类（无认证 / 行业认证 / 最佳雇主 / 两者均有）的关联强度（ε²）为 0.1975，薪资中位数分别为 150、15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>27</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3,410 减少量行</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>The main results are as follows. First, regarding job categories, 10 of the 12 job major categories and 73 of the 78 job subcategories remain significant after field-wise correction (q &lt; 0.05); the "hit/miss" salary diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>208</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>观测—版本—实体 三层简称</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>招聘平台上的一条岗位记录只表示某一时刻的页面状态，而岗位本身是一个有开始、有结束的过程。平台的业务字段记录了这一过程信息：发布时间是招聘方开始接收投递的时间，投递截止日期是招聘方设定的计划结束时间。为了把过程信息纳入分析，同时避免把“投递截止日期被修改”误当成“又招聘了一次”，本文在“观测—版本—实体”的基础上插入两层中间结构，把数据层级扩展为“观测—完整页面版本—候选发布时间段—正式招聘周期—实体”五层：候选发布时间段记录发布时间取值</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>222</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>T3 单独归并措辞</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>**T1 / T2 / T3 三档转换口径。** 设某岗位当前正式周期的结束日为上一周期结束日 End，新候选段的开始时间为 Start，两者之差记为 gap（见式 (8)）：gap 不小于 7 个日历天判为 T1（确认重招），gap 为正且小于 7 个日历天判为 T2（疑似重开），gap 不大于 0 判为 T3（时间冲突，即新发布时间落在上一周期结束日之前或当日）。本文实测 T1 仅 2 个事件（2 个岗位）、T2 为 532 个事件</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>222</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3,410 减少量行</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>**T1 / T2 / T3 三档转换口径。** 设某岗位当前正式周期的结束日为上一周期结束日 End，新候选段的开始时间为 Start，两者之差记为 gap（见式 (8)）：gap 不小于 7 个日历天判为 T1（确认重招），gap 为正且小于 7 个日历天判为 T2（疑似重开），gap 不大于 0 判为 T3（时间冲突，即新发布时间落在上一周期结束日之前或当日）。本文实测 T1 仅 2 个事件（2 个岗位）、T2 为 532 个事件</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>429</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>四层结构残留</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>| 岗位身份 | 实习岗位ID（intern_id）、岗位详情链接 | 岗位实体唯一键与去重依据，贯穿“观测—版本—招聘周期—实体”四层结构；只作标识，不进入模型特征 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>455</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>四层结构残留</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>岗位实体的确认分五层完成，对应“观测—完整页面版本—候选发布时间段—正式招聘周期—实体”五层结构。本节先说明前四层如何逐级压缩与确认，五层各自的粒度、主键与用途见 3.8 节。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>477</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>T3 单独归并措辞</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>T3 的归并使周期数由候选段数 20,556 减少到严格口径的 17,146（减少 3,410 = T2 532 + T3 2,878）。在此基础上本文另建一条宽松口径：把 T1 与 T2 都视为新建正式周期的事件、T3 仍不拆分，得到 17,678 条周期。两条口径下岗位实体数均为 17,144；单周期岗位与多周期岗位分别为 17,142 / 2（严格口径，单岗最多 2 个周期）与 16,636 / 508（宽松口径，单岗最多 3 个</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>477</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3,410 减少量行</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>T3 的归并使周期数由候选段数 20,556 减少到严格口径的 17,146（减少 3,410 = T2 532 + T3 2,878）。在此基础上本文另建一条宽松口径：把 T1 与 T2 都视为新建正式周期的事件、T3 仍不拆分，得到 17,678 条周期。两条口径下岗位实体数均为 17,144；单周期岗位与多周期岗位分别为 17,142 / 2（严格口径，单岗最多 2 个周期）与 16,636 / 508（宽松口径，单岗最多 3 个</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>488</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3,410 减少量行</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>| 候选段 → 严格周期的减少量 | 计数差 | 3,410 | 减少量 = T2 532 + T3 2,878 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>505</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>图 3-3 图题三层简称</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>&gt; 【插图：图 3-3 原始重复观测向岗位实体的分层压缩规模（观测 → 版本 → 实体）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>718</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>T3 单独归并措辞</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>三档转换的实测规模见表 4-2。T1 确认重招只有 2 个事件、涉及 2 个岗位，间隔中位数为 9 个日历天（最小 7、最大 11），样本量过小，只能作个案描述、不据此估计重招比例；T2 疑似重开 532 个事件、涉及 506 个岗位，间隔中位数为 1 个日历天，其中间隔恰为 1 天的占 83.83%（446/532），这种“前一轮刚结束、次日又重新出现”的模式疑为平台字段被重置造成的伪影，故 **T2 不得解释为真实重新招聘**，只在</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>718</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3,410 减少量行</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>三档转换的实测规模见表 4-2。T1 确认重招只有 2 个事件、涉及 2 个岗位，间隔中位数为 9 个日历天（最小 7、最大 11），样本量过小，只能作个案描述、不据此估计重招比例；T2 疑似重开 532 个事件、涉及 506 个岗位，间隔中位数为 1 个日历天，其中间隔恰为 1 天的占 83.83%（446/532），这种“前一轮刚结束、次日又重新出现”的模式疑为平台字段被重置造成的伪影，故 **T2 不得解释为真实重新招聘**，只在</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>735</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>T2 间隔含 0 天</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>| T2 重招间隔（日历天，中位 / 最小 / 最大） | 1 / 0 / 6 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>739</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>T3 归并减少周期数行</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>| T3 归并减少的周期数 | 3,410（= T2 532 + T3 2,878） |</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>739</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3,410 减少量行</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>| T3 归并减少的周期数 | 3,410（= T2 532 + T3 2,878） |</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1431</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>T3 单独归并措辞</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>**第六，招聘生命周期可以被重构并刻画，但严格口径下的多周期样本极少，相关结论只能作辅助发现。** 第一，以发布时间与投递截止日期为业务时间，本文把 17,144 个岗位重构为 20,556 个候选发布时间段，并归并为严格口径 17,146 条、宽松口径 17,678 条正式招聘周期；严格口径下计划持续时长的中位数为 207 天、四分位距为 314 天（P10 为 23 天、P90 为 810 天），首次观测口径下为 204 天与 31</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -844,19 +481,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>减少量正确口径</t>
+          <t>减少量正确统计范围</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T2 与 T3 均在严格口径下并入当前周期，共减少 3,410 个候选发布时间段</t>
+          <t>T2 与 T3 均在严格统计范围下并入当前周期，共减少 3,410 个候选发布时间段</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T2 口径</t>
+          <t>T2 统计范围</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/course-design-2/outputs/tables/ch5/46_stage26_2_wording_consistency_audit.xlsx
+++ b/course-design-2/outputs/tables/ch5/46_stage26_2_wording_consistency_audit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_表述残留命中" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_统一统计范围建议" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_表述残留命中" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_统一统计范围建议" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,9 +426,372 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>行号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>命中类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>原文片段</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3,410 减少量行</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>主要结果如下。第一，岗位类别方面，岗位大类 12 个取值中 10 个、岗位细分类 78 个取值中 73 个在按字段校正后仍显著（q &lt; 0.05），算法方向细分类的“命中/未命中”薪资差异最大（|δ| 达 0.64），算法类岗位薪资中位数（275 元/天）明显高于运营、客服类（150～175 元/天）。第二，公司认证四类（无认证 / 行业认证 / 最佳雇主 / 两者均有）的关联强度（ε²）为 0.1975，薪资中位数分别为 150、15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3,410 减少量行</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The main results are as follows. First, regarding job categories, 10 of the 12 job major categories and 73 of the 78 job subcategories remain significant after field-wise correction (q &lt; 0.05); the "hit/miss" salary diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>208</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>观测—版本—实体 三层简称</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>招聘平台上的一条岗位记录只表示某一时刻的页面状态，而岗位本身是一个有开始、有结束的过程。平台的业务字段记录了这一过程信息：发布时间是招聘方开始接收投递的时间，投递截止日期是招聘方设定的计划结束时间。为了把过程信息纳入分析，同时避免把“投递截止日期被修改”误当成“又招聘了一次”，本文在“观测—版本—实体”的基础上插入两层中间结构，把数据层级扩展为“观测—完整页面版本—候选发布时间段—正式招聘周期—实体”五层：候选发布时间段记录发布时间取值</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>222</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>T3 单独归并措辞</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>**T1 / T2 / T3 三档转换口径。** 设某岗位当前正式周期的结束日为上一周期结束日 End，新候选段的开始时间为 Start，两者之差记为 gap（见式 (8)）：gap 不小于 7 个日历天判为 T1（确认重招），gap 为正且小于 7 个日历天判为 T2（疑似重开），gap 不大于 0 判为 T3（时间冲突，即新发布时间落在上一周期结束日之前或当日）。本文实测 T1 仅 2 个事件（2 个岗位）、T2 为 532 个事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>222</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3,410 减少量行</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>**T1 / T2 / T3 三档转换口径。** 设某岗位当前正式周期的结束日为上一周期结束日 End，新候选段的开始时间为 Start，两者之差记为 gap（见式 (8)）：gap 不小于 7 个日历天判为 T1（确认重招），gap 为正且小于 7 个日历天判为 T2（疑似重开），gap 不大于 0 判为 T3（时间冲突，即新发布时间落在上一周期结束日之前或当日）。本文实测 T1 仅 2 个事件（2 个岗位）、T2 为 532 个事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>429</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>四层结构残留</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>| 岗位身份 | 实习岗位ID（intern_id）、岗位详情链接 | 岗位实体唯一键与去重依据，贯穿“观测—版本—招聘周期—实体”四层结构；只作标识，不进入模型特征 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>455</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>四层结构残留</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>岗位实体的确认分五层完成，对应“观测—完整页面版本—候选发布时间段—正式招聘周期—实体”五层结构。本节先说明前四层如何逐级压缩与确认，五层各自的粒度、主键与用途见 3.8 节。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>477</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>T3 单独归并措辞</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>T3 的归并使周期数由候选段数 20,556 减少到严格口径的 17,146（减少 3,410 = T2 532 + T3 2,878）。在此基础上本文另建一条宽松口径：把 T1 与 T2 都视为新建正式周期的事件、T3 仍不拆分，得到 17,678 条周期。两条口径下岗位实体数均为 17,144；单周期岗位与多周期岗位分别为 17,142 / 2（严格口径，单岗最多 2 个周期）与 16,636 / 508（宽松口径，单岗最多 3 个</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>477</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3,410 减少量行</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>T3 的归并使周期数由候选段数 20,556 减少到严格口径的 17,146（减少 3,410 = T2 532 + T3 2,878）。在此基础上本文另建一条宽松口径：把 T1 与 T2 都视为新建正式周期的事件、T3 仍不拆分，得到 17,678 条周期。两条口径下岗位实体数均为 17,144；单周期岗位与多周期岗位分别为 17,142 / 2（严格口径，单岗最多 2 个周期）与 16,636 / 508（宽松口径，单岗最多 3 个</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>488</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3,410 减少量行</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>| 候选段 → 严格周期的减少量 | 计数差 | 3,410 | 减少量 = T2 532 + T3 2,878 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>505</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>图 3-3 图题三层简称</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>&gt; 【插图：图 3-3 原始重复观测向岗位实体的分层压缩规模（观测 → 版本 → 实体）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>718</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>T3 单独归并措辞</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>三档转换的实测规模见表 4-2。T1 确认重招只有 2 个事件、涉及 2 个岗位，间隔中位数为 9 个日历天（最小 7、最大 11），样本量过小，只能作个案描述、不据此估计重招比例；T2 疑似重开 532 个事件、涉及 506 个岗位，间隔中位数为 1 个日历天，其中间隔恰为 1 天的占 83.83%（446/532），这种“前一轮刚结束、次日又重新出现”的模式疑为平台字段被重置造成的伪影，故 **T2 不得解释为真实重新招聘**，只在</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>718</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3,410 减少量行</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>三档转换的实测规模见表 4-2。T1 确认重招只有 2 个事件、涉及 2 个岗位，间隔中位数为 9 个日历天（最小 7、最大 11），样本量过小，只能作个案描述、不据此估计重招比例；T2 疑似重开 532 个事件、涉及 506 个岗位，间隔中位数为 1 个日历天，其中间隔恰为 1 天的占 83.83%（446/532），这种“前一轮刚结束、次日又重新出现”的模式疑为平台字段被重置造成的伪影，故 **T2 不得解释为真实重新招聘**，只在</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>735</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>T2 间隔含 0 天</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>| T2 重招间隔（日历天，中位 / 最小 / 最大） | 1 / 0 / 6 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>739</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>T3 归并减少周期数行</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>| T3 归并减少的周期数 | 3,410（= T2 532 + T3 2,878） |</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>739</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3,410 减少量行</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>| T3 归并减少的周期数 | 3,410（= T2 532 + T3 2,878） |</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>docs/paper/课程设计论文时序口径收紧修订版_Stage26.1.md</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1431</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>T3 单独归并措辞</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>**第六，招聘生命周期可以被重构并刻画，但严格口径下的多周期样本极少，相关结论只能作辅助发现。** 第一，以发布时间与投递截止日期为业务时间，本文把 17,144 个岗位重构为 20,556 个候选发布时间段，并归并为严格口径 17,146 条、宽松口径 17,678 条正式招聘周期；严格口径下计划持续时长的中位数为 207 天、四分位距为 314 天（P10 为 23 天、P90 为 810 天），首次观测口径下为 204 天与 31</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -481,19 +844,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>减少量正确统计范围</t>
+          <t>减少量正确口径</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T2 与 T3 均在严格统计范围下并入当前周期，共减少 3,410 个候选发布时间段</t>
+          <t>T2 与 T3 均在严格口径下并入当前周期，共减少 3,410 个候选发布时间段</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T2 统计范围</t>
+          <t>T2 口径</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
